--- a/artfynd/A 41648-2023 artfynd.xlsx
+++ b/artfynd/A 41648-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41648-2023 artfynd.xlsx
+++ b/artfynd/A 41648-2023 artfynd.xlsx
@@ -1102,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117967951</v>
+        <v>117968018</v>
       </c>
       <c r="B6" t="n">
         <v>97836</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512045</v>
+        <v>512061</v>
       </c>
       <c r="R6" t="n">
-        <v>6943984</v>
+        <v>6944007</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117967908</v>
+        <v>117967829</v>
       </c>
       <c r="B7" t="n">
         <v>97836</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512052</v>
+        <v>512174</v>
       </c>
       <c r="R7" t="n">
-        <v>6944004</v>
+        <v>6944034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>4 florala.</t>
+          <t>0 florala.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117968094</v>
+        <v>117967951</v>
       </c>
       <c r="B8" t="n">
-        <v>97857</v>
+        <v>97836</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,30 +1354,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512134</v>
+        <v>512045</v>
       </c>
       <c r="R8" t="n">
-        <v>6944016</v>
+        <v>6943984</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,6 +1430,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 floral.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117968018</v>
+        <v>117968094</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>97857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,30 +1474,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1509,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512061</v>
+        <v>512134</v>
       </c>
       <c r="R9" t="n">
-        <v>6944007</v>
+        <v>6944016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,11 +1550,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 floral.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,7 +1577,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117967829</v>
+        <v>117967908</v>
       </c>
       <c r="B10" t="n">
         <v>97836</v>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512174</v>
+        <v>512052</v>
       </c>
       <c r="R10" t="n">
-        <v>6944034</v>
+        <v>6944004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0 florala.</t>
+          <t>4 florala.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 41648-2023 artfynd.xlsx
+++ b/artfynd/A 41648-2023 artfynd.xlsx
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117968018</v>
+        <v>117967908</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512061</v>
+        <v>512052</v>
       </c>
       <c r="R6" t="n">
-        <v>6944007</v>
+        <v>6944004</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 floral.</t>
+          <t>4 florala.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117967829</v>
+        <v>117967951</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512174</v>
+        <v>512045</v>
       </c>
       <c r="R7" t="n">
-        <v>6944034</v>
+        <v>6943984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0 florala.</t>
+          <t>1 floral.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117967951</v>
+        <v>117968094</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>97859</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,30 +1354,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512045</v>
+        <v>512134</v>
       </c>
       <c r="R8" t="n">
-        <v>6943984</v>
+        <v>6944016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,11 +1430,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 floral.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117968094</v>
+        <v>117968018</v>
       </c>
       <c r="B9" t="n">
-        <v>97857</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,30 +1469,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512134</v>
+        <v>512061</v>
       </c>
       <c r="R9" t="n">
-        <v>6944016</v>
+        <v>6944007</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,6 +1545,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 floral.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117967908</v>
+        <v>117967829</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512052</v>
+        <v>512174</v>
       </c>
       <c r="R10" t="n">
-        <v>6944004</v>
+        <v>6944034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>4 florala.</t>
+          <t>0 florala.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 41648-2023 artfynd.xlsx
+++ b/artfynd/A 41648-2023 artfynd.xlsx
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111879329</v>
+        <v>111879379</v>
       </c>
       <c r="B2" t="n">
-        <v>96720</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512170</v>
+        <v>512177</v>
       </c>
       <c r="R2" t="n">
-        <v>6944037</v>
+        <v>6944053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,12 +779,7 @@
         <v>111879311</v>
       </c>
       <c r="B3" t="n">
-        <v>96720</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,42 +878,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111879379</v>
+        <v>111879329</v>
       </c>
       <c r="B4" t="n">
-        <v>89033</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512177</v>
+        <v>512170</v>
       </c>
       <c r="R4" t="n">
-        <v>6944053</v>
+        <v>6944037</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,12 +983,7 @@
         <v>111879393</v>
       </c>
       <c r="B5" t="n">
-        <v>96720</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,12 +1085,7 @@
         <v>117967829</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,15 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117967951</v>
+        <v>117967908</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,7 +1227,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512045</v>
+        <v>512052</v>
       </c>
       <c r="R7" t="n">
-        <v>6943984</v>
+        <v>6944004</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 floral.</t>
+          <t>4 florala.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,42 +1312,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117968094</v>
+        <v>117967951</v>
       </c>
       <c r="B8" t="n">
-        <v>97867</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1394,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512134</v>
+        <v>512045</v>
       </c>
       <c r="R8" t="n">
-        <v>6944016</v>
+        <v>6943984</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,6 +1395,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 floral.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,12 +1430,7 @@
         <v>117968018</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,42 +1542,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117967908</v>
+        <v>117968094</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1629,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512052</v>
+        <v>512134</v>
       </c>
       <c r="R10" t="n">
-        <v>6944004</v>
+        <v>6944016</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,11 +1625,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4 florala.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 41648-2023 artfynd.xlsx
+++ b/artfynd/A 41648-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111879379</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111879311</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111879329</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111879393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967829</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967908</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117967951</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117968018</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,8 +1694,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117968094</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>